--- a/data/trans_orig/P79A1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A1_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>964</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>615</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>964</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>964</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>34535</t>
+          <t>39222</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29171</t>
+          <t>33853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>42875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>39414</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>39414</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39414</t>
+          <t>44580</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>53565</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>57330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
